--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/31.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/31.xlsx
@@ -426,13 +426,13 @@
         <v>-20.89342255506635</v>
       </c>
       <c r="E2">
-        <v>-10.67404098934336</v>
+        <v>-10.55623273803381</v>
       </c>
       <c r="F2">
-        <v>0.1685191258737091</v>
+        <v>-1.145845924526951</v>
       </c>
       <c r="G2">
-        <v>-12.20905474022164</v>
+        <v>-12.35971435716834</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.454160345064</v>
       </c>
       <c r="E3">
-        <v>-11.30453136848328</v>
+        <v>-12.70105388228672</v>
       </c>
       <c r="F3">
-        <v>0.06582529949295354</v>
+        <v>-1.286342811109247</v>
       </c>
       <c r="G3">
-        <v>-12.11073484825083</v>
+        <v>-12.04286535415023</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.91101904275678</v>
       </c>
       <c r="E4">
-        <v>-11.71290009754698</v>
+        <v>-13.23953472653881</v>
       </c>
       <c r="F4">
-        <v>-0.08003401531901956</v>
+        <v>-1.031616384258135</v>
       </c>
       <c r="G4">
-        <v>-10.97791913344086</v>
+        <v>-11.46306965058443</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.3143951709491</v>
       </c>
       <c r="E5">
-        <v>-12.89674735805419</v>
+        <v>-13.46627542010286</v>
       </c>
       <c r="F5">
-        <v>0.1515742644314647</v>
+        <v>-1.00833432359526</v>
       </c>
       <c r="G5">
-        <v>-10.57309569326216</v>
+        <v>-11.22088007056797</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.6828574085523</v>
       </c>
       <c r="E6">
-        <v>-13.50964914414833</v>
+        <v>-12.26874763961848</v>
       </c>
       <c r="F6">
-        <v>0.3771628779973636</v>
+        <v>-0.9467170775432572</v>
       </c>
       <c r="G6">
-        <v>-10.13780530248555</v>
+        <v>-10.42007896789151</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.04996990631766</v>
       </c>
       <c r="E7">
-        <v>-14.35180039840677</v>
+        <v>-14.19293700174368</v>
       </c>
       <c r="F7">
-        <v>0.3513627249289396</v>
+        <v>-1.246809552195089</v>
       </c>
       <c r="G7">
-        <v>-10.13394520638676</v>
+        <v>-10.23175527434452</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.42359550613047</v>
       </c>
       <c r="E8">
-        <v>-14.81949213697095</v>
+        <v>-15.00486974894894</v>
       </c>
       <c r="F8">
-        <v>0.262363203598989</v>
+        <v>-1.488065768382431</v>
       </c>
       <c r="G8">
-        <v>-9.83486390127792</v>
+        <v>-9.425303070432523</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.82411754159201</v>
       </c>
       <c r="E9">
-        <v>-15.14930089894958</v>
+        <v>-16.39594903699516</v>
       </c>
       <c r="F9">
-        <v>0.2663058394754755</v>
+        <v>-0.9842604099746647</v>
       </c>
       <c r="G9">
-        <v>-9.476527141561666</v>
+        <v>-8.802781466136892</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.25452548651609</v>
       </c>
       <c r="E10">
-        <v>-15.83975733089908</v>
+        <v>-16.80031006656207</v>
       </c>
       <c r="F10">
-        <v>0.5943697280057992</v>
+        <v>-0.8851220033740708</v>
       </c>
       <c r="G10">
-        <v>-8.000278743053242</v>
+        <v>-8.50262423372779</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.70890382488541</v>
       </c>
       <c r="E11">
-        <v>-16.77167199693756</v>
+        <v>-19.15240399462006</v>
       </c>
       <c r="F11">
-        <v>0.5408848118295783</v>
+        <v>-0.83646739023994</v>
       </c>
       <c r="G11">
-        <v>-7.329489384795036</v>
+        <v>-8.627031224548062</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.18001435429739</v>
       </c>
       <c r="E12">
-        <v>-17.10351404374564</v>
+        <v>-18.54839613147699</v>
       </c>
       <c r="F12">
-        <v>0.8396746883659616</v>
+        <v>-0.7470165127240892</v>
       </c>
       <c r="G12">
-        <v>-6.913525958876689</v>
+        <v>-7.199037337820054</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.63664708410513</v>
       </c>
       <c r="E13">
-        <v>-17.42219634508742</v>
+        <v>-19.93785875430247</v>
       </c>
       <c r="F13">
-        <v>0.5847518819813355</v>
+        <v>-0.4608258085979843</v>
       </c>
       <c r="G13">
-        <v>-5.95798664714915</v>
+        <v>-7.358085877163259</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.06328356740781</v>
       </c>
       <c r="E14">
-        <v>-19.41280483548313</v>
+        <v>-20.57073111077043</v>
       </c>
       <c r="F14">
-        <v>0.8281215537128308</v>
+        <v>-0.2821505235121904</v>
       </c>
       <c r="G14">
-        <v>-5.569709313575729</v>
+        <v>-6.578617929941859</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.44474588199713</v>
       </c>
       <c r="E15">
-        <v>-20.47854949387029</v>
+        <v>-20.88106743451608</v>
       </c>
       <c r="F15">
-        <v>1.221202113042648</v>
+        <v>-0.4356900201610872</v>
       </c>
       <c r="G15">
-        <v>-5.064281705004118</v>
+        <v>-6.32501027836045</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.76837602644837</v>
       </c>
       <c r="E16">
-        <v>-20.27825508851103</v>
+        <v>-21.77334889603943</v>
       </c>
       <c r="F16">
-        <v>1.25854589852871</v>
+        <v>0.06420358463554354</v>
       </c>
       <c r="G16">
-        <v>-4.487203959326061</v>
+        <v>-5.253942858948965</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.04497909593157</v>
       </c>
       <c r="E17">
-        <v>-22.29425020419374</v>
+        <v>-23.05132048879607</v>
       </c>
       <c r="F17">
-        <v>1.155356372196422</v>
+        <v>0.2992429632518274</v>
       </c>
       <c r="G17">
-        <v>-4.178972306346678</v>
+        <v>-4.655018823257257</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.28439975259039</v>
       </c>
       <c r="E18">
-        <v>-23.22954311184194</v>
+        <v>-24.77521997403602</v>
       </c>
       <c r="F18">
-        <v>1.47052493531028</v>
+        <v>0.511683650307748</v>
       </c>
       <c r="G18">
-        <v>-4.435953403832604</v>
+        <v>-5.122166593758275</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.50303919888963</v>
       </c>
       <c r="E19">
-        <v>-24.13690892028485</v>
+        <v>-25.24803341670287</v>
       </c>
       <c r="F19">
-        <v>1.69879080372623</v>
+        <v>0.7121119279950604</v>
       </c>
       <c r="G19">
-        <v>-4.229818975284344</v>
+        <v>-4.844855436115685</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.725444665540575</v>
       </c>
       <c r="E20">
-        <v>-23.8779390772082</v>
+        <v>-26.11405878592975</v>
       </c>
       <c r="F20">
-        <v>1.962555440236754</v>
+        <v>1.204308722042655</v>
       </c>
       <c r="G20">
-        <v>-3.592413158244149</v>
+        <v>-4.4562271847151</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.965170784250596</v>
       </c>
       <c r="E21">
-        <v>-24.89302369687156</v>
+        <v>-25.69489870330578</v>
       </c>
       <c r="F21">
-        <v>2.069037491167241</v>
+        <v>1.032861470754927</v>
       </c>
       <c r="G21">
-        <v>-4.049443901577154</v>
+        <v>-3.9834581078884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.25134003533625</v>
       </c>
       <c r="E22">
-        <v>-25.74021514270054</v>
+        <v>-26.60597333196096</v>
       </c>
       <c r="F22">
-        <v>2.339692832115842</v>
+        <v>1.511001291097082</v>
       </c>
       <c r="G22">
-        <v>-3.397223393248719</v>
+        <v>-3.326013558698996</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.608419639575095</v>
       </c>
       <c r="E23">
-        <v>-26.10676794277741</v>
+        <v>-26.19895861662556</v>
       </c>
       <c r="F23">
-        <v>2.002141753299079</v>
+        <v>1.234785558679372</v>
       </c>
       <c r="G23">
-        <v>-3.66167639201678</v>
+        <v>-4.774873813961031</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.05167039598907</v>
       </c>
       <c r="E24">
-        <v>-26.08847290778642</v>
+        <v>-27.33162959237208</v>
       </c>
       <c r="F24">
-        <v>2.113783518102067</v>
+        <v>1.283696732171804</v>
       </c>
       <c r="G24">
-        <v>-2.659200165633454</v>
+        <v>-4.58754659462137</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.59797851322265</v>
       </c>
       <c r="E25">
-        <v>-26.21268894981682</v>
+        <v>-27.28921137634223</v>
       </c>
       <c r="F25">
-        <v>2.074539285517477</v>
+        <v>1.472890991947947</v>
       </c>
       <c r="G25">
-        <v>-4.245795668056867</v>
+        <v>-4.079924094357223</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.249532944297508</v>
       </c>
       <c r="E26">
-        <v>-26.78716210548186</v>
+        <v>-28.04892176129104</v>
       </c>
       <c r="F26">
-        <v>2.477809408707232</v>
+        <v>1.144710701032838</v>
       </c>
       <c r="G26">
-        <v>-3.488372643581473</v>
+        <v>-3.64832165131136</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.00122262048588</v>
       </c>
       <c r="E27">
-        <v>-26.96325634574413</v>
+        <v>-28.18761986319796</v>
       </c>
       <c r="F27">
-        <v>2.436295725545818</v>
+        <v>1.145329930045775</v>
       </c>
       <c r="G27">
-        <v>-3.329171819143461</v>
+        <v>-4.23751599366315</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.84559398712106</v>
       </c>
       <c r="E28">
-        <v>-27.02082230732963</v>
+        <v>-28.43946188818654</v>
       </c>
       <c r="F28">
-        <v>2.255363659530523</v>
+        <v>1.096836854915019</v>
       </c>
       <c r="G28">
-        <v>-3.028759674727836</v>
+        <v>-4.350511534009554</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.76294373994812</v>
       </c>
       <c r="E29">
-        <v>-26.21349501819018</v>
+        <v>-27.77677858732608</v>
       </c>
       <c r="F29">
-        <v>2.268468825980784</v>
+        <v>1.116428880794921</v>
       </c>
       <c r="G29">
-        <v>-3.518895873453553</v>
+        <v>-4.372175744018545</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.73966962647222</v>
       </c>
       <c r="E30">
-        <v>-26.57624390010061</v>
+        <v>-27.97205997195885</v>
       </c>
       <c r="F30">
-        <v>2.261033326707796</v>
+        <v>1.150375617092365</v>
       </c>
       <c r="G30">
-        <v>-3.509397918301384</v>
+        <v>-3.953504291849074</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.760895340222809</v>
       </c>
       <c r="E31">
-        <v>-26.04947821810637</v>
+        <v>-27.74899187081501</v>
       </c>
       <c r="F31">
-        <v>2.033109538769581</v>
+        <v>1.146237393535322</v>
       </c>
       <c r="G31">
-        <v>-3.172801511141525</v>
+        <v>-4.629199878596481</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.808784909802434</v>
       </c>
       <c r="E32">
-        <v>-25.66346203674453</v>
+        <v>-25.70615196121484</v>
       </c>
       <c r="F32">
-        <v>2.08514378032726</v>
+        <v>1.168581900296257</v>
       </c>
       <c r="G32">
-        <v>-3.960198214929481</v>
+        <v>-4.012584287542908</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.87290722616557</v>
       </c>
       <c r="E33">
-        <v>-25.98838457526888</v>
+        <v>-26.42070440335915</v>
       </c>
       <c r="F33">
-        <v>2.051328491620797</v>
+        <v>1.41996037284213</v>
       </c>
       <c r="G33">
-        <v>-3.833093129494703</v>
+        <v>-3.85013912847641</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.946309856530101</v>
       </c>
       <c r="E34">
-        <v>-25.87857813753089</v>
+        <v>-26.51047687208721</v>
       </c>
       <c r="F34">
-        <v>2.25456230433731</v>
+        <v>0.9859473504218644</v>
       </c>
       <c r="G34">
-        <v>-3.730615192326563</v>
+        <v>-4.027958461027284</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.024682353431482</v>
       </c>
       <c r="E35">
-        <v>-24.08273931420509</v>
+        <v>-26.23432147015146</v>
       </c>
       <c r="F35">
-        <v>2.253779953615083</v>
+        <v>1.001014728501355</v>
       </c>
       <c r="G35">
-        <v>-3.076514294131823</v>
+        <v>-4.266079380575982</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.111191304608414</v>
       </c>
       <c r="E36">
-        <v>-24.20368579800195</v>
+        <v>-26.47159086578334</v>
       </c>
       <c r="F36">
-        <v>2.241832476189008</v>
+        <v>1.360892893313985</v>
       </c>
       <c r="G36">
-        <v>-3.092080479257476</v>
+        <v>-3.397815980900249</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.208223141378334</v>
       </c>
       <c r="E37">
-        <v>-23.75244600550764</v>
+        <v>-24.49486667669516</v>
       </c>
       <c r="F37">
-        <v>1.993863722479077</v>
+        <v>1.28177094577863</v>
       </c>
       <c r="G37">
-        <v>-2.90914304330289</v>
+        <v>-2.708884833086836</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.320850605435686</v>
       </c>
       <c r="E38">
-        <v>-23.41414635476463</v>
+        <v>-24.87800727706212</v>
       </c>
       <c r="F38">
-        <v>2.473740868210468</v>
+        <v>0.8448344022384633</v>
       </c>
       <c r="G38">
-        <v>-2.840747172461547</v>
+        <v>-4.054896370080333</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.459119838712213</v>
       </c>
       <c r="E39">
-        <v>-22.77761499129846</v>
+        <v>-25.0436588562627</v>
       </c>
       <c r="F39">
-        <v>2.015368865104829</v>
+        <v>1.292736525537132</v>
       </c>
       <c r="G39">
-        <v>-3.276706293437091</v>
+        <v>-3.301280472975101</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.626442359239036</v>
       </c>
       <c r="E40">
-        <v>-22.32910134015677</v>
+        <v>-23.68983079540358</v>
       </c>
       <c r="F40">
-        <v>2.145932748185488</v>
+        <v>1.79435003495793</v>
       </c>
       <c r="G40">
-        <v>-3.135547942188107</v>
+        <v>-3.16428678801452</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.827090767183661</v>
       </c>
       <c r="E41">
-        <v>-21.92325949958935</v>
+        <v>-23.11605502473572</v>
       </c>
       <c r="F41">
-        <v>2.065585012271583</v>
+        <v>1.182789326063664</v>
       </c>
       <c r="G41">
-        <v>-2.568722956045173</v>
+        <v>-3.058048071113768</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.067978906019265</v>
       </c>
       <c r="E42">
-        <v>-21.45372467210405</v>
+        <v>-23.22976047859431</v>
       </c>
       <c r="F42">
-        <v>2.024888521362535</v>
+        <v>1.019963769779588</v>
       </c>
       <c r="G42">
-        <v>-2.616302116535578</v>
+        <v>-3.947836637885842</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.349500362998866</v>
       </c>
       <c r="E43">
-        <v>-21.08947686529709</v>
+        <v>-22.19051192162603</v>
       </c>
       <c r="F43">
-        <v>2.272052752467423</v>
+        <v>0.8976779175189313</v>
       </c>
       <c r="G43">
-        <v>-3.238376797183409</v>
+        <v>-4.414252777822681</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.676039918236735</v>
       </c>
       <c r="E44">
-        <v>-19.81097091260754</v>
+        <v>-22.28800543853716</v>
       </c>
       <c r="F44">
-        <v>2.251317290916575</v>
+        <v>0.8780478826970595</v>
       </c>
       <c r="G44">
-        <v>-2.759632185658324</v>
+        <v>-3.780998384888731</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.045476482855404</v>
       </c>
       <c r="E45">
-        <v>-19.9702328149833</v>
+        <v>-21.29914068337822</v>
       </c>
       <c r="F45">
-        <v>1.870873121086049</v>
+        <v>1.164747748274978</v>
       </c>
       <c r="G45">
-        <v>-3.398881976563894</v>
+        <v>-3.683628619487687</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.449262237942772</v>
       </c>
       <c r="E46">
-        <v>-19.60621596035073</v>
+        <v>-21.16203207584798</v>
       </c>
       <c r="F46">
-        <v>1.950839183874333</v>
+        <v>1.316013835082261</v>
       </c>
       <c r="G46">
-        <v>-3.609184381946096</v>
+        <v>-3.742139201348766</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.882978656481027</v>
       </c>
       <c r="E47">
-        <v>-18.26009083377865</v>
+        <v>-20.45708905554794</v>
       </c>
       <c r="F47">
-        <v>2.533953367115476</v>
+        <v>0.8642553878794973</v>
       </c>
       <c r="G47">
-        <v>-4.019404011353807</v>
+        <v>-4.727354243290332</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.332718652687841</v>
       </c>
       <c r="E48">
-        <v>-18.32815379811394</v>
+        <v>-21.14810701827439</v>
       </c>
       <c r="F48">
-        <v>2.246493322698146</v>
+        <v>1.504978457500666</v>
       </c>
       <c r="G48">
-        <v>-2.781677108404331</v>
+        <v>-4.2285675890705</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.787282078811719</v>
       </c>
       <c r="E49">
-        <v>-17.44417755792065</v>
+        <v>-19.62849605246847</v>
       </c>
       <c r="F49">
-        <v>2.303039542408912</v>
+        <v>0.9976826112552707</v>
       </c>
       <c r="G49">
-        <v>-3.635430386981438</v>
+        <v>-4.743268035697609</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.23984480686462</v>
       </c>
       <c r="E50">
-        <v>-17.66201527158563</v>
+        <v>-18.48807232922081</v>
       </c>
       <c r="F50">
-        <v>2.227851520367508</v>
+        <v>0.6550557549795235</v>
       </c>
       <c r="G50">
-        <v>-4.028080951212236</v>
+        <v>-5.239008988021312</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.67774814545341</v>
       </c>
       <c r="E51">
-        <v>-16.31974387639408</v>
+        <v>-18.05122855559688</v>
       </c>
       <c r="F51">
-        <v>1.978983221697608</v>
+        <v>0.9292554297668785</v>
       </c>
       <c r="G51">
-        <v>-3.460411775956788</v>
+        <v>-4.697006472331833</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.09877017951991</v>
       </c>
       <c r="E52">
-        <v>-16.17260017046285</v>
+        <v>-19.0972879374727</v>
       </c>
       <c r="F52">
-        <v>1.968304292709799</v>
+        <v>1.27440196215409</v>
       </c>
       <c r="G52">
-        <v>-4.393750569297975</v>
+        <v>-5.097085900752757</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.49787891985218</v>
       </c>
       <c r="E53">
-        <v>-16.12727920259409</v>
+        <v>-18.09246936838474</v>
       </c>
       <c r="F53">
-        <v>2.153490192813965</v>
+        <v>1.165542768644529</v>
       </c>
       <c r="G53">
-        <v>-4.010300011120811</v>
+        <v>-4.925794964005326</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.86949035821289</v>
       </c>
       <c r="E54">
-        <v>-14.34966295867515</v>
+        <v>-16.22873060578792</v>
       </c>
       <c r="F54">
-        <v>2.183322461143097</v>
+        <v>1.549889189850697</v>
       </c>
       <c r="G54">
-        <v>-5.17715144462003</v>
+        <v>-5.187629321251824</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.21792545161468</v>
       </c>
       <c r="E55">
-        <v>-14.95791853043741</v>
+        <v>-16.75887000091788</v>
       </c>
       <c r="F55">
-        <v>2.139754711409358</v>
+        <v>1.246333942214757</v>
       </c>
       <c r="G55">
-        <v>-5.065781382133408</v>
+        <v>-4.485902914929127</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.5377096820952</v>
       </c>
       <c r="E56">
-        <v>-14.99216737935742</v>
+        <v>-16.48256515933987</v>
       </c>
       <c r="F56">
-        <v>2.007773411534381</v>
+        <v>1.221067498039836</v>
       </c>
       <c r="G56">
-        <v>-4.713734658941771</v>
+        <v>-5.586235556907771</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.82802812971686</v>
       </c>
       <c r="E57">
-        <v>-14.73672521753276</v>
+        <v>-15.68962936059679</v>
       </c>
       <c r="F57">
-        <v>2.523295026304568</v>
+        <v>0.9550381620702327</v>
       </c>
       <c r="G57">
-        <v>-5.134001794061169</v>
+        <v>-5.461189630798419</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.08973500741206</v>
       </c>
       <c r="E58">
-        <v>-14.03792733646113</v>
+        <v>-14.78196920134339</v>
       </c>
       <c r="F58">
-        <v>1.942253914106736</v>
+        <v>0.8149514553200364</v>
       </c>
       <c r="G58">
-        <v>-5.289660334772162</v>
+        <v>-6.349024975702323</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.31791591712847</v>
       </c>
       <c r="E59">
-        <v>-14.44573453474787</v>
+        <v>-14.68899510149191</v>
       </c>
       <c r="F59">
-        <v>2.291209259220579</v>
+        <v>1.218836056404981</v>
       </c>
       <c r="G59">
-        <v>-5.243120685581087</v>
+        <v>-5.844365413695823</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.51602454312676</v>
       </c>
       <c r="E60">
-        <v>-13.86621213056427</v>
+        <v>-15.27124817550213</v>
       </c>
       <c r="F60">
-        <v>1.544732643390026</v>
+        <v>1.042064385829546</v>
       </c>
       <c r="G60">
-        <v>-5.999302255479255</v>
+        <v>-6.924987067533646</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.68036401483124</v>
       </c>
       <c r="E61">
-        <v>-14.22544691664475</v>
+        <v>-14.58267106026582</v>
       </c>
       <c r="F61">
-        <v>2.235434304290633</v>
+        <v>0.9407436324774763</v>
       </c>
       <c r="G61">
-        <v>-5.912145523066862</v>
+        <v>-5.546419625706956</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.80876511285318</v>
       </c>
       <c r="E62">
-        <v>-13.87186819459986</v>
+        <v>-15.61023615429431</v>
       </c>
       <c r="F62">
-        <v>2.006569795038647</v>
+        <v>0.6846473000095096</v>
       </c>
       <c r="G62">
-        <v>-5.793776967310221</v>
+        <v>-6.916823262233804</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.90651097323666</v>
       </c>
       <c r="E63">
-        <v>-13.05817839947962</v>
+        <v>-14.84394136813836</v>
       </c>
       <c r="F63">
-        <v>1.860238535863873</v>
+        <v>0.7021805081993396</v>
       </c>
       <c r="G63">
-        <v>-5.813779283458497</v>
+        <v>-6.64007158678735</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.97019030541725</v>
       </c>
       <c r="E64">
-        <v>-12.64324791157881</v>
+        <v>-12.03245639437225</v>
       </c>
       <c r="F64">
-        <v>1.714350714345422</v>
+        <v>0.9563637239214555</v>
       </c>
       <c r="G64">
-        <v>-5.748021917411953</v>
+        <v>-7.04347811347524</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.00542375237012</v>
       </c>
       <c r="E65">
-        <v>-11.40931572854677</v>
+        <v>-13.46769736094127</v>
       </c>
       <c r="F65">
-        <v>1.826640214867825</v>
+        <v>0.5660023876484479</v>
       </c>
       <c r="G65">
-        <v>-5.79282684074045</v>
+        <v>-6.414196375188416</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.01761503590146</v>
       </c>
       <c r="E66">
-        <v>-12.1381102214452</v>
+        <v>-12.18587656527811</v>
       </c>
       <c r="F66">
-        <v>1.486642310411707</v>
+        <v>0.8635268831583951</v>
       </c>
       <c r="G66">
-        <v>-5.332416030411848</v>
+        <v>-7.26355655983491</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.01088536511654</v>
       </c>
       <c r="E67">
-        <v>-12.94668284093677</v>
+        <v>-13.04237855366686</v>
       </c>
       <c r="F67">
-        <v>1.988061024004906</v>
+        <v>0.7358073359018654</v>
       </c>
       <c r="G67">
-        <v>-6.485051981365437</v>
+        <v>-7.105762717251088</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.99721863034301</v>
       </c>
       <c r="E68">
-        <v>-11.79376505790195</v>
+        <v>-12.58398377224043</v>
       </c>
       <c r="F68">
-        <v>1.627083767286962</v>
+        <v>0.4224212337958345</v>
       </c>
       <c r="G68">
-        <v>-6.622492589973819</v>
+        <v>-7.714581973559677</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.97835787180422</v>
       </c>
       <c r="E69">
-        <v>-12.74172863582362</v>
+        <v>-13.26656518789059</v>
       </c>
       <c r="F69">
-        <v>1.521073660719277</v>
+        <v>0.4838713988737582</v>
       </c>
       <c r="G69">
-        <v>-6.685134732667909</v>
+        <v>-7.459775904493053</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.95804235217172</v>
       </c>
       <c r="E70">
-        <v>-11.50853006558082</v>
+        <v>-13.4578569869226</v>
       </c>
       <c r="F70">
-        <v>1.368794002126112</v>
+        <v>0.3503657820551704</v>
       </c>
       <c r="G70">
-        <v>-6.80718130451868</v>
+        <v>-7.33637200897118</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.94301317320268</v>
       </c>
       <c r="E71">
-        <v>-11.40298945035805</v>
+        <v>-12.25912916082619</v>
       </c>
       <c r="F71">
-        <v>1.03510716574302</v>
+        <v>0.613288678871639</v>
       </c>
       <c r="G71">
-        <v>-6.586397711959146</v>
+        <v>-7.508954058478926</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.92811826178988</v>
       </c>
       <c r="E72">
-        <v>-12.41907486277711</v>
+        <v>-13.46102239025396</v>
       </c>
       <c r="F72">
-        <v>0.9880758511722151</v>
+        <v>0.2140015760592145</v>
       </c>
       <c r="G72">
-        <v>-6.828014567597315</v>
+        <v>-7.937173123983654</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.91466464964079</v>
       </c>
       <c r="E73">
-        <v>-11.40793907244844</v>
+        <v>-13.31770524485921</v>
       </c>
       <c r="F73">
-        <v>1.193918027531457</v>
+        <v>-0.005124725518733704</v>
       </c>
       <c r="G73">
-        <v>-6.312622216952497</v>
+        <v>-7.464708617346567</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.89736924904817</v>
       </c>
       <c r="E74">
-        <v>-11.98689994585508</v>
+        <v>-13.68364670094504</v>
       </c>
       <c r="F74">
-        <v>1.193138844221061</v>
+        <v>0.1006858341036067</v>
       </c>
       <c r="G74">
-        <v>-6.744486193095963</v>
+        <v>-6.994415828583241</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.87093555871158</v>
       </c>
       <c r="E75">
-        <v>-12.71594350482394</v>
+        <v>-12.84542616212526</v>
       </c>
       <c r="F75">
-        <v>1.078814281597318</v>
+        <v>-0.07152713899423657</v>
       </c>
       <c r="G75">
-        <v>-6.34699892183229</v>
+        <v>-5.610213838248712</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.83571707495922</v>
       </c>
       <c r="E76">
-        <v>-12.4226161294511</v>
+        <v>-13.27709841843243</v>
       </c>
       <c r="F76">
-        <v>0.61918481599482</v>
+        <v>-0.3396493423310927</v>
       </c>
       <c r="G76">
-        <v>-5.894758537894609</v>
+        <v>-7.371874299334324</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.78296763279412</v>
       </c>
       <c r="E77">
-        <v>-13.31282354987894</v>
+        <v>-14.83650561381776</v>
       </c>
       <c r="F77">
-        <v>0.5663222962433667</v>
+        <v>0.004879544749097285</v>
       </c>
       <c r="G77">
-        <v>-6.35408348928633</v>
+        <v>-6.937438029306845</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.71058712243377</v>
       </c>
       <c r="E78">
-        <v>-13.50205489323746</v>
+        <v>-13.72415842941766</v>
       </c>
       <c r="F78">
-        <v>0.6650315185408765</v>
+        <v>-0.335891208193755</v>
       </c>
       <c r="G78">
-        <v>-6.505537637162448</v>
+        <v>-6.738768880949642</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.62084727014973</v>
       </c>
       <c r="E79">
-        <v>-13.11196761374273</v>
+        <v>-13.89208330257009</v>
       </c>
       <c r="F79">
-        <v>0.5245061252521035</v>
+        <v>-0.06971062830922753</v>
       </c>
       <c r="G79">
-        <v>-6.508950809613435</v>
+        <v>-6.815729133101079</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.50871240730012</v>
       </c>
       <c r="E80">
-        <v>-14.85201110882003</v>
+        <v>-16.02657499761151</v>
       </c>
       <c r="F80">
-        <v>0.5167538847960274</v>
+        <v>-0.2538306943323023</v>
       </c>
       <c r="G80">
-        <v>-6.530012500334279</v>
+        <v>-6.101035319901058</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.37842536492321</v>
       </c>
       <c r="E81">
-        <v>-15.63579939006761</v>
+        <v>-15.41611858748152</v>
       </c>
       <c r="F81">
-        <v>0.604236215858987</v>
+        <v>-0.4469169113956374</v>
       </c>
       <c r="G81">
-        <v>-6.167679912152126</v>
+        <v>-6.271597936629849</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.22808001449511</v>
       </c>
       <c r="E82">
-        <v>-16.55415127645312</v>
+        <v>-15.64266908513725</v>
       </c>
       <c r="F82">
-        <v>0.4734371524498854</v>
+        <v>-0.5326650844811909</v>
       </c>
       <c r="G82">
-        <v>-5.212567660799153</v>
+        <v>-6.009293481916774</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.06005672382449</v>
       </c>
       <c r="E83">
-        <v>-17.75749361756335</v>
+        <v>-17.69785361488233</v>
       </c>
       <c r="F83">
-        <v>0.4681214435447129</v>
+        <v>-0.1677143096214091</v>
       </c>
       <c r="G83">
-        <v>-5.820675149816799</v>
+        <v>-5.827915312911185</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.88181896438831</v>
       </c>
       <c r="E84">
-        <v>-17.54151710671553</v>
+        <v>-17.43006683291275</v>
       </c>
       <c r="F84">
-        <v>0.3075590030137999</v>
+        <v>-0.6054577513254918</v>
       </c>
       <c r="G84">
-        <v>-5.422820407998266</v>
+        <v>-5.614822117639378</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.69192314773514</v>
       </c>
       <c r="E85">
-        <v>-17.91039754243234</v>
+        <v>-19.07722226914472</v>
       </c>
       <c r="F85">
-        <v>0.3647767140327117</v>
+        <v>-0.6357089098692584</v>
       </c>
       <c r="G85">
-        <v>-5.217553342381295</v>
+        <v>-5.000202785545985</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.49460302361224</v>
       </c>
       <c r="E86">
-        <v>-19.54448380267817</v>
+        <v>-18.7859191216533</v>
       </c>
       <c r="F86">
-        <v>0.5181166637362631</v>
+        <v>-0.3660354665882294</v>
       </c>
       <c r="G86">
-        <v>-5.264943801775963</v>
+        <v>-5.321534267224265</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.29368077412363</v>
       </c>
       <c r="E87">
-        <v>-21.27508995792348</v>
+        <v>-21.60893359024294</v>
       </c>
       <c r="F87">
-        <v>0.3981002620524308</v>
+        <v>-0.2858001737943207</v>
       </c>
       <c r="G87">
-        <v>-5.027183731691045</v>
+        <v>-5.166375618889703</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.08446205992365</v>
       </c>
       <c r="E88">
-        <v>-22.81007962145945</v>
+        <v>-21.66183975207456</v>
       </c>
       <c r="F88">
-        <v>0.3815845849132706</v>
+        <v>-0.2432372854639278</v>
       </c>
       <c r="G88">
-        <v>-4.286068454542101</v>
+        <v>-5.403619243870494</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.86800001871462</v>
       </c>
       <c r="E89">
-        <v>-24.45175107566813</v>
+        <v>-24.04433332614604</v>
       </c>
       <c r="F89">
-        <v>0.4380231126217862</v>
+        <v>-0.4760333446509916</v>
       </c>
       <c r="G89">
-        <v>-4.525043494839931</v>
+        <v>-5.954401326330119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.63493855519534</v>
       </c>
       <c r="E90">
-        <v>-24.73786006347274</v>
+        <v>-24.28076948256052</v>
       </c>
       <c r="F90">
-        <v>0.4196901329446591</v>
+        <v>-0.941380780461184</v>
       </c>
       <c r="G90">
-        <v>-4.176075578999816</v>
+        <v>-5.076302295857212</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.3815780101263</v>
       </c>
       <c r="E91">
-        <v>-26.59156825614256</v>
+        <v>-27.11870980147944</v>
       </c>
       <c r="F91">
-        <v>0.2797229959910785</v>
+        <v>-0.507435065542325</v>
       </c>
       <c r="G91">
-        <v>-4.54049050032617</v>
+        <v>-5.418414071885496</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.10497980857955</v>
       </c>
       <c r="E92">
-        <v>-29.16230143776489</v>
+        <v>-29.95650520923011</v>
       </c>
       <c r="F92">
-        <v>0.1889766470363981</v>
+        <v>-0.6734185314217872</v>
       </c>
       <c r="G92">
-        <v>-4.772506773900452</v>
+        <v>-3.719892335324864</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.79508835608598</v>
       </c>
       <c r="E93">
-        <v>-31.34070121678467</v>
+        <v>-30.40634343901905</v>
       </c>
       <c r="F93">
-        <v>0.08035421756119503</v>
+        <v>-0.7106989686712317</v>
       </c>
       <c r="G93">
-        <v>-3.792595225912799</v>
+        <v>-4.972983480122097</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.45107196163775</v>
       </c>
       <c r="E94">
-        <v>-33.57142072025208</v>
+        <v>-33.19639061683285</v>
       </c>
       <c r="F94">
-        <v>-0.0469337698333774</v>
+        <v>-0.8775756446870018</v>
       </c>
       <c r="G94">
-        <v>-5.01762287617363</v>
+        <v>-4.151988049656079</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.07443889328731</v>
       </c>
       <c r="E95">
-        <v>-35.28339899766684</v>
+        <v>-34.88634918938531</v>
       </c>
       <c r="F95">
-        <v>0.2108951369060801</v>
+        <v>-0.9328881574896399</v>
       </c>
       <c r="G95">
-        <v>-4.742920428415985</v>
+        <v>-4.165640739460033</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.667612309511927</v>
       </c>
       <c r="E96">
-        <v>-37.080039360892</v>
+        <v>-35.99545625063293</v>
       </c>
       <c r="F96">
-        <v>0.4024261547604537</v>
+        <v>-0.7922827870521372</v>
       </c>
       <c r="G96">
-        <v>-4.428603992735422</v>
+        <v>-4.202450695311189</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.245006417739775</v>
       </c>
       <c r="E97">
-        <v>-40.17362562296594</v>
+        <v>-39.43730707050376</v>
       </c>
       <c r="F97">
-        <v>-0.08133423787559535</v>
+        <v>-0.6259247747236736</v>
       </c>
       <c r="G97">
-        <v>-4.885955858985737</v>
+        <v>-5.5609396784422</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.81410407166833</v>
       </c>
       <c r="E98">
-        <v>-42.97376903357983</v>
+        <v>-40.92414999839018</v>
       </c>
       <c r="F98">
-        <v>0.2362130515232528</v>
+        <v>-0.8135685864086011</v>
       </c>
       <c r="G98">
-        <v>-4.990526060934696</v>
+        <v>-4.65882264008188</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.39643230642287</v>
       </c>
       <c r="E99">
-        <v>-44.78781232241647</v>
+        <v>-44.35414980178293</v>
       </c>
       <c r="F99">
-        <v>0.08424063187768344</v>
+        <v>-0.4679231866580262</v>
       </c>
       <c r="G99">
-        <v>-4.848877748945899</v>
+        <v>-5.912350776890297</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.009589522357937</v>
       </c>
       <c r="E100">
-        <v>-48.31801593441396</v>
+        <v>-47.00560982530299</v>
       </c>
       <c r="F100">
-        <v>0.4286760803088626</v>
+        <v>-1.001480044393238</v>
       </c>
       <c r="G100">
-        <v>-4.89529490795202</v>
+        <v>-5.696036420808778</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.672809870768852</v>
       </c>
       <c r="E101">
-        <v>-49.89742879584667</v>
+        <v>-49.09384315835606</v>
       </c>
       <c r="F101">
-        <v>-0.1916749882690502</v>
+        <v>-1.073451559720384</v>
       </c>
       <c r="G101">
-        <v>-5.738086970248601</v>
+        <v>-4.883817246567367</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.394775310378019</v>
       </c>
       <c r="E102">
-        <v>-51.32885678730123</v>
+        <v>-51.71054940810425</v>
       </c>
       <c r="F102">
-        <v>0.2149874329915756</v>
+        <v>-1.262148535839078</v>
       </c>
       <c r="G102">
-        <v>-5.286707328151131</v>
+        <v>-5.517727127518093</v>
       </c>
     </row>
   </sheetData>
